--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:14:04+00:00</t>
+    <t>2026-08-31T21:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:22:01+00:00</t>
+    <t>2026-08-31T21:48:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:48:04+00:00</t>
+    <t>2026-08-31T22:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:00:30+00:00</t>
+    <t>2026-09-01T09:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:07:35+00:00</t>
+    <t>2026-09-04T10:28:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,8 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">
-**Disclaimer** 
+    <t>**Disclaimer** 
  (Punkte übernommen aus der Policy Liste ([MII SharePoint, TF Consent Umsetzung](https://tmfev.sharepoint.com/:f:/r/sites/tmf/mi-i/Taskforce%20Consent%20Umsetzung/02_Dokumente/Policies?csf=1&amp;web=1&amp;e=C0xLim "")))
 1. Diese Liste fasst erforderliche
                     Einwilligungsmodule und zugeordnete Einwilligungspolicies für die technische Abbildung der "MII Mustertexte Patienteneinwilligung" in den aktuell verfügbaren Versionen zusammen. 
@@ -109,8 +108,7 @@
                             2.16.840.1.113883.3.1937.777.24.5.3.2**.1** (.1 wird aus dem [MII Consent: Answer ValueSet](https://art-decor.org/art-decor/decor-valuesets--mide-?id=2.16.840.1.113883.3.1937.777.24.11.30&amp;effectiveDate=2021-03-23T23:45:09&amp;language=de-DE "") angehängt)  
  Beispiel 2:  
  2.16.840.1.113883.3.1937.777.24.5.3.4.2
-                    bedeutet, dass der Patient der Policy IDAT_zusammenfuehren_Dritte nicht zugestimmt hat.
-</t>
+                    bedeutet, dass der Patient der Policy IDAT_zusammenfuehren_Dritte nicht zugestimmt hat.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:28:22+00:00</t>
+    <t>2026-09-04T11:15:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:15:21+00:00</t>
+    <t>2026-09-04T11:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:42:10+00:00</t>
+    <t>2026-09-04T11:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:09+00:00</t>
+    <t>2026-09-04T12:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:01:13+00:00</t>
+    <t>2026-09-04T12:10:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:10:03+00:00</t>
+    <t>2026-09-04T12:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:19:56+00:00</t>
+    <t>2026-09-04T13:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
